--- a/Workspace/키워드_순위_작업표.xlsx
+++ b/Workspace/키워드_순위_작업표.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>7위, 9위</t>
+          <t>6위, 8위</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>9위</t>
+          <t>10위</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>미노출 (범위 밖)</t>
+          <t>5위</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 11:19:13</t>
         </is>
       </c>
     </row>

--- a/Workspace/키워드_순위_작업표.xlsx
+++ b/Workspace/키워드_순위_작업표.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>7위, 9위</t>
+          <t>6위, 8위</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>9위</t>
+          <t>10위</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>미노출 (범위 밖)</t>
+          <t>5위</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-08 20:29:00</t>
+          <t>2026-06-09 13:03:18</t>
         </is>
       </c>
     </row>

--- a/Workspace/키워드_순위_작업표.xlsx
+++ b/Workspace/키워드_순위_작업표.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>6위, 8위</t>
+          <t>5위, 7위</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>10위</t>
+          <t>8위</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>5위</t>
+          <t>2위, 5위</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 13:03:18</t>
+          <t>2026-06-09 17:33:27</t>
         </is>
       </c>
     </row>

--- a/Workspace/키워드_순위_작업표.xlsx
+++ b/Workspace/키워드_순위_작업표.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>5위, 7위</t>
+          <t>5위, 6위, 18위, 19위, 22위, 26위, 29위</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>5위</t>
+          <t>5위, 11위, 16위, 18위</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4위</t>
+          <t>4위, 23위</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2위, 5위</t>
+          <t>2위, 16위, 27위, 28위</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 17:33:27</t>
+          <t>2026-06-09 20:59:45</t>
         </is>
       </c>
     </row>

--- a/Workspace/키워드_순위_작업표.xlsx
+++ b/Workspace/키워드_순위_작업표.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>8위</t>
+          <t>5위</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>4위, 23위</t>
+          <t>3위, 25위</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2위, 16위, 27위, 28위</t>
+          <t>1위, 16위, 26위, 27위</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-09 20:59:45</t>
+          <t>2026-06-10 09:01:51</t>
         </is>
       </c>
     </row>
